--- a/Sample_Codes/logs.xlsx
+++ b/Sample_Codes/logs.xlsx
@@ -88,6 +88,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -180,7 +181,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:B26"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="81.05"/>
   </cols>
